--- a/NBFC-MF/Borrowers/Template_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Template_Weekly.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>Date</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Principal Outstanding</t>
+  </si>
+  <si>
+    <t>Payment Day</t>
   </si>
 </sst>
 </file>
@@ -337,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -422,6 +425,9 @@
     </xf>
     <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1252,7 +1258,7 @@
         <v>9999.9999999995434</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>46174</v>
       </c>
@@ -1282,12 +1288,9 @@
         <v>8641.0100516592465</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="16">
-        <f>IF(A2,A2, "")</f>
-        <v>46174</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="19">
@@ -1318,12 +1321,12 @@
         <f t="shared" si="2"/>
         <v>9313.7601803447487</v>
       </c>
-      <c r="J17" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="18">
-        <f xml:space="preserve"> IF(A2,(K16 + (17*7)),"")</f>
-        <v>46293</v>
+      <c r="J17" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="16">
+        <f>IF(A2,A2, "")</f>
+        <v>46174</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -1355,9 +1358,16 @@
         <f t="shared" si="2"/>
         <v>9999.9999999995434</v>
       </c>
+      <c r="J18" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="18">
+        <f xml:space="preserve"> IF(A2,(K17 + (17*7)),"")</f>
+        <v>46293</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7yI+izlIteEFB5AAwDvg1y34kMaRdn2zkdICuBVpUy+l8hBGD2XadCAmNwRvlqpKFFdwkO6lgwHbJqgs4Mqxsg==" saltValue="k1ngp1D5U8OI70ytiKa8RQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fo2FK/OGc9mhEwmwYJgN4ko2hBr/ptI1SfQMiNu1sM3tkayvRhUpVkZ5lsJOIWAvWpWeYNFuWS6X3x49SQWuCQ==" saltValue="C9NhUIZE+m9H7Y+CLL0OUw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
